--- a/AAII_Financials/Quarterly/NXT_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/NXT_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="199" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="92">
   <si>
     <t>NXT</t>
   </si>
@@ -656,328 +656,341 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Y102"/>
+  <dimension ref="A5:Z102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:26" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46206</v>
+      </c>
+      <c r="E7" s="2">
         <v>46112</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45926</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45835</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45562</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45471</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45198</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44834</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44743</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44651</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44561</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44470</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44379</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44286</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44196</v>
       </c>
     </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>935200</v>
+      </c>
+      <c r="E8" s="3">
         <v>880500</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>909400</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>905300</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>864300</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>924300</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>679400</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>635600</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>719900</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>736500</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>710400</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>573400</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>479500</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>518400</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>513400</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>467100</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>403200</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>439800</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>337600</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>338700</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>341500</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>318100</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>291500</v>
       </c>
     </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>599300</v>
+      </c>
+      <c r="E9" s="3">
         <v>963000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>621200</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>612400</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>582500</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>843500</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>438500</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>410800</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>482500</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>517500</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>500700</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>424200</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>365800</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>428100</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>431100</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>402600</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>353400</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>400900</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>303800</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>302000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>303900</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>256300</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>234500</v>
       </c>
     </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>335900</v>
+      </c>
+      <c r="E10" s="3">
         <v>-82500</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>288100</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>292900</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>281700</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>80800</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>240900</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>224800</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>237400</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>219100</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>209700</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>149100</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>113700</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>90300</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>82300</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>64500</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>49800</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>38900</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>33800</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>36700</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>37600</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>61800</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>57000</v>
       </c>
     </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1003,79 +1016,83 @@
       <c r="W11" s="3"/>
       <c r="X11" s="3"/>
       <c r="Y11" s="3"/>
-    </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z11" s="3"/>
+    </row>
+    <row r="12" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>44500</v>
+      </c>
+      <c r="E12" s="3">
         <v>43200</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>29300</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>26900</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>21600</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>23600</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>20100</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>19200</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>16500</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>13100</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>12900</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>7100</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>5600</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>8300</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>5000</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>4300</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>4000</v>
-      </c>
-      <c r="T12" s="3">
-        <v>3600</v>
       </c>
       <c r="U12" s="3">
         <v>3600</v>
       </c>
       <c r="V12" s="3">
+        <v>3600</v>
+      </c>
+      <c r="W12" s="3">
         <v>3400</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>3600</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>3800</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>3500</v>
       </c>
     </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1145,38 +1162,41 @@
       <c r="Y13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
+        <v>4100</v>
+      </c>
+      <c r="E14" s="3">
         <v>13100</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>400</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>7700</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>1100</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>600</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>1000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>2200</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>1500</v>
       </c>
-      <c r="L14" s="3" t="s">
-        <v>11</v>
-      </c>
       <c r="M14" s="3" t="s">
         <v>11</v>
       </c>
@@ -1186,14 +1206,14 @@
       <c r="O14" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="P14" s="3">
+      <c r="P14" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="Q14" s="3">
         <v>1400</v>
       </c>
-      <c r="Q14" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="R14" s="3">
-        <v>0</v>
+      <c r="R14" s="3" t="s">
+        <v>11</v>
       </c>
       <c r="S14" s="3">
         <v>0</v>
@@ -1216,43 +1236,46 @@
       <c r="Y14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3">
+        <v>8800</v>
+      </c>
+      <c r="E15" s="3">
         <v>9000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>8400</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>7400</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>5800</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>5100</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>4400</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>2900</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>900</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>1200</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>1100</v>
-      </c>
-      <c r="N15" s="3">
-        <v>1000</v>
       </c>
       <c r="O15" s="3">
         <v>1000</v>
@@ -1261,34 +1284,37 @@
         <v>1000</v>
       </c>
       <c r="Q15" s="3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="R15" s="3">
+        <v>0</v>
+      </c>
+      <c r="S15" s="3">
         <v>600</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>400</v>
-      </c>
-      <c r="T15" s="3">
-        <v>500</v>
       </c>
       <c r="U15" s="3">
         <v>500</v>
       </c>
       <c r="V15" s="3">
+        <v>500</v>
+      </c>
+      <c r="W15" s="3">
         <v>1800</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>1700</v>
       </c>
-      <c r="X15" s="3" t="s">
-        <v>11</v>
-      </c>
       <c r="Y15" s="3" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z15" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="16" spans="1:26" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1311,150 +1337,157 @@
       <c r="W16" s="3"/>
       <c r="X16" s="3"/>
       <c r="Y16" s="3"/>
-    </row>
-    <row r="17" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z16" s="3"/>
+    </row>
+    <row r="17" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>740100</v>
+      </c>
+      <c r="E17" s="3">
         <v>720700</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>732800</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>721300</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>676900</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>728400</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>528100</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>499900</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>558300</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>465800</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>562000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>479300</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>405700</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>476400</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>454700</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>427700</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>373500</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>432200</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>320500</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>318600</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>320300</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>275900</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>250600</v>
       </c>
     </row>
-    <row r="18" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>195100</v>
+      </c>
+      <c r="E18" s="3">
         <v>159900</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>176500</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>183900</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>187300</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>196000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>151300</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>135700</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>161600</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>270700</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>148500</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>94100</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>73900</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>42000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>58700</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>39400</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>29700</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>7600</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>17100</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>20100</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>21200</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>42200</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>40900</v>
       </c>
     </row>
-    <row r="19" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1480,150 +1513,157 @@
       <c r="W19" s="3"/>
       <c r="X19" s="3"/>
       <c r="Y19" s="3"/>
-    </row>
-    <row r="20" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z19" s="3"/>
+    </row>
+    <row r="20" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E20" s="3">
         <v>-4300</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>4900</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-800</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>300</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>2800</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-8000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-4100</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>9500</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-25000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-18100</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>8700</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-2000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-1700</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>2300</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-1300</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>100</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-400</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-100</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-200</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-100</v>
       </c>
-      <c r="X20" s="3">
-        <v>0</v>
-      </c>
       <c r="Y20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z20" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="21" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>202800</v>
+      </c>
+      <c r="E21" s="3">
         <v>173200</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>180100</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>192100</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>192800</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>198300</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>163700</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>142700</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>153000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>296900</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>167700</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>86300</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>76900</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>44700</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>62000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>39500</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>31100</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>8400</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>18200</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>24200</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>25500</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>59000</v>
       </c>
-      <c r="Y21" s="3" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="22" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z21" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="22" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1634,43 +1674,43 @@
         <v>300</v>
       </c>
       <c r="F22" s="3">
+        <v>300</v>
+      </c>
+      <c r="G22" s="3">
         <v>700</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>1200</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>2400</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>3800</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>3700</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>3300</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>3800</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>3200</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>3600</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>3100</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>1800</v>
       </c>
-      <c r="Q22" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="R22" s="3">
-        <v>0</v>
+      <c r="R22" s="3" t="s">
+        <v>11</v>
       </c>
       <c r="S22" s="3">
         <v>0</v>
@@ -1693,150 +1733,159 @@
       <c r="Y22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>198900</v>
+      </c>
+      <c r="E23" s="3">
         <v>159600</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>180500</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>182700</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>191000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>198700</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>160200</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>137200</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>151900</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>283100</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>166800</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>85400</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>72700</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>40100</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>61000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>38200</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>29800</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>7100</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>17000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>19900</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>21100</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>42200</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>40800</v>
       </c>
     </row>
-    <row r="24" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>33600</v>
+      </c>
+      <c r="E24" s="3">
         <v>9000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>49300</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>35900</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>33800</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>40800</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>42800</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>19900</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>27200</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>59900</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>38800</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>4000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>9100</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>12500</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>18400</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>11100</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>5700</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>1400</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>4500</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>4000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>4400</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>9000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>8700</v>
       </c>
     </row>
-    <row r="25" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1906,150 +1955,159 @@
       <c r="Y25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>165400</v>
+      </c>
+      <c r="E26" s="3">
         <v>150600</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>131200</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>146900</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>157200</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>157800</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>117400</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>117300</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>124800</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>223200</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>128000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>81400</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>63600</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>27500</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>42600</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>27100</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>24100</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>5800</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>12500</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>15900</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>16700</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>33200</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>32100</v>
       </c>
     </row>
-    <row r="27" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>165400</v>
+      </c>
+      <c r="E27" s="3">
         <v>150600</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>131200</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>146900</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>157200</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>156800</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>115300</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>115400</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>121700</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>205200</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>41400</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>39300</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>20400</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>1100</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>42600</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>27100</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>24100</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>5800</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>12500</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>15900</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>16700</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>33200</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>32100</v>
       </c>
     </row>
-    <row r="28" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2119,8 +2177,11 @@
       <c r="Y28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2190,8 +2251,11 @@
       <c r="Y29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2261,8 +2325,11 @@
       <c r="Y30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2332,150 +2399,159 @@
       <c r="Y31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="E32" s="3">
         <v>4300</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-4900</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>800</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-300</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-2800</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>8000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>4100</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-9500</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>25000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>18100</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-8700</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>2000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>1700</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-2300</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>1300</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-100</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>400</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>100</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>200</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>100</v>
       </c>
-      <c r="X32" s="3">
-        <v>0</v>
-      </c>
       <c r="Y32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z32" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="33" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>165400</v>
+      </c>
+      <c r="E33" s="3">
         <v>150600</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>131200</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>146900</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>157200</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>156800</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>115300</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>115400</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>121700</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>205200</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>41400</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>39300</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>20400</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>25100</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>42600</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>27100</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>24100</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>5800</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>12500</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>15900</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>16700</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>33200</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>32100</v>
       </c>
     </row>
-    <row r="34" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2545,155 +2621,164 @@
       <c r="Y34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>165400</v>
+      </c>
+      <c r="E35" s="3">
         <v>150600</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>131200</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>146900</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>157200</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>156800</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>115300</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>115400</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>121700</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>205200</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>41400</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>39300</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>20400</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>25100</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>42600</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>27100</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>24100</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>5800</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>12500</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>15900</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>16700</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>33200</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>32100</v>
       </c>
     </row>
-    <row r="37" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46206</v>
+      </c>
+      <c r="E38" s="2">
         <v>46112</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45926</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45835</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45562</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45471</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45198</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44834</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44743</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44651</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44561</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44470</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44379</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44286</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44196</v>
       </c>
     </row>
-    <row r="39" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2719,8 +2804,9 @@
       <c r="W39" s="3"/>
       <c r="X39" s="3"/>
       <c r="Y39" s="3"/>
-    </row>
-    <row r="40" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z39" s="3"/>
+    </row>
+    <row r="40" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2746,84 +2832,88 @@
       <c r="W40" s="3"/>
       <c r="X40" s="3"/>
       <c r="Y40" s="3"/>
-    </row>
-    <row r="41" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z40" s="3"/>
+    </row>
+    <row r="41" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1213900</v>
+      </c>
+      <c r="E41" s="3">
         <v>1095000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>952600</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>845300</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>743400</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>766100</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>693500</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>561900</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>471900</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>474100</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>367800</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>372900</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>355100</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>130000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>100100</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>84200</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>31100</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>29100</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>129700</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>191300</v>
       </c>
-      <c r="W41" s="3" t="s">
-        <v>11</v>
-      </c>
       <c r="X41" s="3" t="s">
         <v>11</v>
       </c>
       <c r="Y41" s="3" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="42" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z41" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="42" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>51300</v>
+        <v>0</v>
       </c>
       <c r="E42" s="3">
         <v>0</v>
@@ -2835,7 +2925,7 @@
         <v>0</v>
       </c>
       <c r="H42" s="3">
-        <v>50200</v>
+        <v>0</v>
       </c>
       <c r="I42" s="3">
         <v>0</v>
@@ -2888,301 +2978,316 @@
       <c r="Y42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>1363700</v>
+      </c>
+      <c r="E43" s="3">
         <v>1302900</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>1196700</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>1219000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>1159500</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>1094000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>946800</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>884800</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>931800</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>905200</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>716800</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>663100</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>542900</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>569100</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>553500</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>564700</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>517100</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>460700</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>340000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>335400</v>
       </c>
-      <c r="W43" s="3" t="s">
-        <v>11</v>
-      </c>
       <c r="X43" s="3" t="s">
         <v>11</v>
       </c>
       <c r="Y43" s="3" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="44" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z43" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="44" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>261600</v>
+      </c>
+      <c r="E44" s="3">
         <v>262300</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>275300</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>221200</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>227100</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>209400</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>217300</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>179300</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>166000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>201700</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>202700</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>196200</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>136700</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>138100</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>251200</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>240000</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>200900</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>172200</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>108300</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>94500</v>
       </c>
-      <c r="W44" s="3" t="s">
-        <v>11</v>
-      </c>
       <c r="X44" s="3" t="s">
         <v>11</v>
       </c>
       <c r="Y44" s="3" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="45" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z44" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="45" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>135100</v>
+        <v>189100</v>
       </c>
       <c r="E45" s="3">
+        <v>186400</v>
+      </c>
+      <c r="F45" s="3">
         <v>134900</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>153100</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>102900</v>
       </c>
-      <c r="H45" s="3">
-        <v>38300</v>
-      </c>
       <c r="I45" s="3">
+        <v>88500</v>
+      </c>
+      <c r="J45" s="3">
         <v>136800</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>158800</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>127700</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>187200</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>131700</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>106600</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>82200</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>35100</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>49600</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>96500</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>77800</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>52100</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>73700</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>61300</v>
       </c>
-      <c r="W45" s="3" t="s">
-        <v>11</v>
-      </c>
       <c r="X45" s="3" t="s">
         <v>11</v>
       </c>
       <c r="Y45" s="3" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="46" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z45" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="46" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>3028200</v>
+      </c>
+      <c r="E46" s="3">
         <v>2846600</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>2559600</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>2438700</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>2232900</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>2158000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>1994500</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>1784700</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>1697400</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>1768200</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>1419000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>1338800</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>1116800</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>872300</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>954300</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>985500</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>826900</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>714100</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>651700</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>682400</v>
       </c>
-      <c r="W46" s="3" t="s">
-        <v>11</v>
-      </c>
       <c r="X46" s="3" t="s">
         <v>11</v>
       </c>
       <c r="Y46" s="3" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="47" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z46" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="47" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
+      <c r="D47" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E47" s="3">
         <v>5700</v>
       </c>
-      <c r="E47" s="3" t="s">
-        <v>11</v>
-      </c>
       <c r="F47" s="3" t="s">
         <v>11</v>
       </c>
@@ -3216,8 +3321,8 @@
       <c r="P47" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="Q47" s="3">
-        <v>0</v>
+      <c r="Q47" s="3" t="s">
+        <v>11</v>
       </c>
       <c r="R47" s="3">
         <v>0</v>
@@ -3243,150 +3348,159 @@
       <c r="Y47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>89200</v>
+      </c>
+      <c r="E48" s="3">
         <v>129200</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>84800</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>84900</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>72400</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>93200</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>48000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>47200</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>35300</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>26600</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>8400</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>7500</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>6900</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>10600</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>7900</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>7500</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>7100</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>11800</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>6800</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>5600</v>
       </c>
-      <c r="W48" s="3" t="s">
-        <v>11</v>
-      </c>
       <c r="X48" s="3" t="s">
         <v>11</v>
       </c>
       <c r="Y48" s="3" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="49" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z48" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="49" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>569600</v>
+      </c>
+      <c r="E49" s="3">
         <v>567000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>565900</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>555400</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>513900</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>424300</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>418100</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>419900</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>374800</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>266700</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>266800</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>266300</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>266400</v>
-      </c>
-      <c r="P49" s="3">
-        <v>266500</v>
       </c>
       <c r="Q49" s="3">
         <v>266500</v>
       </c>
       <c r="R49" s="3">
+        <v>266500</v>
+      </c>
+      <c r="S49" s="3">
         <v>266600</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>267100</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>267700</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>268800</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>272400</v>
       </c>
-      <c r="W49" s="3" t="s">
-        <v>11</v>
-      </c>
       <c r="X49" s="3" t="s">
         <v>11</v>
       </c>
       <c r="Y49" s="3" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="50" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z49" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="50" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3456,8 +3570,11 @@
       <c r="Y50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3527,79 +3644,85 @@
       <c r="Y51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>66200</v>
+      </c>
+      <c r="E52" s="3">
         <v>10900</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>72200</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>76200</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>59400</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>18300</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>50700</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>38500</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>51500</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>19000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>16500</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>16000</v>
       </c>
-      <c r="O52" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="P52" s="3">
+      <c r="P52" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="Q52" s="3">
         <v>13200</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>30900</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>28200</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>28300</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>23800</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>17600</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>16500</v>
       </c>
-      <c r="W52" s="3" t="s">
-        <v>11</v>
-      </c>
       <c r="X52" s="3" t="s">
         <v>11</v>
       </c>
       <c r="Y52" s="3" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="53" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z52" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="53" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3669,79 +3792,85 @@
       <c r="Y53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>4262200</v>
+      </c>
+      <c r="E54" s="3">
         <v>4073200</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>3800100</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>3668900</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>3389900</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>3192500</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>2983600</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>2768700</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>2626900</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>2518800</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>2095100</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>2033600</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>1656900</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>1419700</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>1259700</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>1287800</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>1129500</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>1017300</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>944900</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>977000</v>
       </c>
-      <c r="W54" s="3" t="s">
-        <v>11</v>
-      </c>
       <c r="X54" s="3" t="s">
         <v>11</v>
       </c>
       <c r="Y54" s="3" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="55" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z54" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="55" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3767,8 +3896,9 @@
       <c r="W55" s="3"/>
       <c r="X55" s="3"/>
       <c r="Y55" s="3"/>
-    </row>
-    <row r="56" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z55" s="3"/>
+    </row>
+    <row r="56" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3794,88 +3924,92 @@
       <c r="W56" s="3"/>
       <c r="X56" s="3"/>
       <c r="Y56" s="3"/>
-    </row>
-    <row r="57" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z56" s="3"/>
+    </row>
+    <row r="57" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>536000</v>
+      </c>
+      <c r="E57" s="3">
         <v>533500</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>560100</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>553600</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>581500</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>585300</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>377500</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>406500</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>387400</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>456600</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>374900</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>403500</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>293500</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>211400</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>311400</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>355800</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>295200</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>266600</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>246800</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>232500</v>
       </c>
-      <c r="W57" s="3" t="s">
-        <v>11</v>
-      </c>
       <c r="X57" s="3" t="s">
         <v>11</v>
       </c>
       <c r="Y57" s="3" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="58" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z57" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="58" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>0</v>
+      </c>
+      <c r="E58" s="3">
         <v>11900</v>
       </c>
-      <c r="E58" s="3">
-        <v>0</v>
-      </c>
       <c r="F58" s="3">
         <v>0</v>
       </c>
@@ -3883,23 +4017,23 @@
         <v>0</v>
       </c>
       <c r="H58" s="3">
+        <v>0</v>
+      </c>
+      <c r="I58" s="3">
         <v>8500</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>6600</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>5600</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>4700</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>7700</v>
       </c>
-      <c r="M58" s="3">
-        <v>0</v>
-      </c>
       <c r="N58" s="3">
         <v>0</v>
       </c>
@@ -3907,13 +4041,13 @@
         <v>0</v>
       </c>
       <c r="P58" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q58" s="3">
         <v>1900</v>
       </c>
-      <c r="Q58" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="R58" s="3">
-        <v>0</v>
+      <c r="R58" s="3" t="s">
+        <v>11</v>
       </c>
       <c r="S58" s="3">
         <v>0</v>
@@ -3936,195 +4070,204 @@
       <c r="Y58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>477400</v>
+      </c>
+      <c r="E59" s="3">
         <v>488300</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>418100</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>462600</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>364500</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>342700</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>447800</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>317000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>326300</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>344800</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>314300</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>301400</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>325400</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>234400</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>293300</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>295900</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>265600</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>206800</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>191400</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>195300</v>
       </c>
-      <c r="W59" s="3" t="s">
-        <v>11</v>
-      </c>
       <c r="X59" s="3" t="s">
         <v>11</v>
       </c>
       <c r="Y59" s="3" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="60" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z59" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="60" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1126400</v>
+      </c>
+      <c r="E60" s="3">
         <v>1163900</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>1084800</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>1119800</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>1032000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>1033500</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>904600</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>806300</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>803000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>891500</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>759400</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>772200</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>676100</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>507400</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>604600</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>651800</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>560800</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>473400</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>438200</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>427900</v>
       </c>
-      <c r="W60" s="3" t="s">
-        <v>11</v>
-      </c>
       <c r="X60" s="3" t="s">
         <v>11</v>
       </c>
       <c r="Y60" s="3" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="61" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z60" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="61" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>38400</v>
+      </c>
+      <c r="E61" s="3">
         <v>41000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>44800</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>45700</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>26600</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>25600</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>138800</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>140500</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>142200</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>157600</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>144800</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>145600</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>147300</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>148600</v>
       </c>
-      <c r="Q61" s="3">
-        <v>0</v>
-      </c>
       <c r="R61" s="3">
         <v>0</v>
       </c>
@@ -4149,79 +4292,85 @@
       <c r="Y61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>427300</v>
+      </c>
+      <c r="E62" s="3">
         <v>431500</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>422000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>418800</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>422800</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>408600</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>420400</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>444100</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>444400</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>408400</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>370600</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>382200</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>240700</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>243000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>35900</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>32900</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>41500</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>42800</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>43100</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>41100</v>
       </c>
-      <c r="W62" s="3" t="s">
-        <v>11</v>
-      </c>
       <c r="X62" s="3" t="s">
         <v>11</v>
       </c>
       <c r="Y62" s="3" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="63" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z62" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="63" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4291,8 +4440,11 @@
       <c r="Y63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4362,8 +4514,11 @@
       <c r="Y64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4433,79 +4588,85 @@
       <c r="Y65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1705100</v>
+      </c>
+      <c r="E66" s="3">
         <v>1738800</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>1649200</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>1683200</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>1582800</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>1564400</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>1558600</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>1486300</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>1490300</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>1526800</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>1343600</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>1358400</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>1099700</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>934800</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>640500</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>684700</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>602400</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>516200</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>481300</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>468900</v>
       </c>
-      <c r="W66" s="3" t="s">
-        <v>11</v>
-      </c>
       <c r="X66" s="3" t="s">
         <v>11</v>
       </c>
       <c r="Y66" s="3" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="67" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z66" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="67" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4531,8 +4692,9 @@
       <c r="W67" s="3"/>
       <c r="X67" s="3"/>
       <c r="Y67" s="3"/>
-    </row>
-    <row r="68" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z67" s="3"/>
+    </row>
+    <row r="68" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4602,8 +4764,11 @@
       <c r="Y68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4673,8 +4838,11 @@
       <c r="Y69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4718,20 +4886,20 @@
         <v>0</v>
       </c>
       <c r="Q70" s="3">
+        <v>0</v>
+      </c>
+      <c r="R70" s="3">
         <v>522900</v>
       </c>
-      <c r="R70" s="3">
+      <c r="S70" s="3">
         <v>516700</v>
       </c>
-      <c r="S70" s="3">
+      <c r="T70" s="3">
         <v>510400</v>
       </c>
-      <c r="T70" s="3">
+      <c r="U70" s="3">
         <v>504200</v>
       </c>
-      <c r="U70" s="3">
-        <v>0</v>
-      </c>
       <c r="V70" s="3">
         <v>0</v>
       </c>
@@ -4744,8 +4912,11 @@
       <c r="Y70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4815,79 +4986,85 @@
       <c r="Y71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-1806200</v>
+      </c>
+      <c r="E72" s="3">
         <v>-1971500</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-2122100</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-2253400</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-2400200</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-2557400</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-2714200</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-2829500</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-2944900</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-3066600</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-3272000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-3313100</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-3352400</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-3075800</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>96300</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>86400</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>16700</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-3000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>463600</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>508000</v>
       </c>
-      <c r="W72" s="3" t="s">
-        <v>11</v>
-      </c>
       <c r="X72" s="3" t="s">
         <v>11</v>
       </c>
       <c r="Y72" s="3" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="73" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z72" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="73" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4957,8 +5134,11 @@
       <c r="Y73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5028,8 +5208,11 @@
       <c r="Y74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5099,79 +5282,85 @@
       <c r="Y75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>2557100</v>
+      </c>
+      <c r="E76" s="3">
         <v>2334400</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>2150900</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>1985700</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>1807100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>1628100</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>1406600</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>1266000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>1121400</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>961000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>-3117000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>-2641000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>-3352400</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>-3075800</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>96300</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>86400</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>16700</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>-3000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>463600</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>508000</v>
       </c>
-      <c r="W76" s="3" t="s">
-        <v>11</v>
-      </c>
       <c r="X76" s="3" t="s">
         <v>11</v>
       </c>
       <c r="Y76" s="3" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="77" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z76" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="77" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5241,155 +5430,164 @@
       <c r="Y77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46206</v>
+      </c>
+      <c r="E80" s="2">
         <v>46112</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45926</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45835</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45562</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45471</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45198</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44834</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44743</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44651</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44561</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44470</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44379</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44286</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44196</v>
       </c>
     </row>
-    <row r="81" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>165400</v>
+      </c>
+      <c r="E81" s="3">
         <v>150600</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>131200</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>146900</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>157200</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>156800</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>115300</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>115400</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>121700</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>205200</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>41400</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>39300</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>20400</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>25100</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>42600</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>27100</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>24100</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>5800</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>12500</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>15900</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>16700</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>33200</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>32100</v>
       </c>
     </row>
-    <row r="82" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5415,79 +5613,83 @@
       <c r="W82" s="3"/>
       <c r="X82" s="3"/>
       <c r="Y82" s="3"/>
-    </row>
-    <row r="83" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z82" s="3"/>
+    </row>
+    <row r="83" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>3700</v>
+      </c>
+      <c r="E83" s="3">
         <v>3300</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>2600</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>1100</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>900</v>
-      </c>
-      <c r="H83" s="3">
-        <v>1100</v>
       </c>
       <c r="I83" s="3">
         <v>1100</v>
       </c>
       <c r="J83" s="3">
+        <v>1100</v>
+      </c>
+      <c r="K83" s="3">
         <v>900</v>
-      </c>
-      <c r="K83" s="3">
-        <v>1000</v>
       </c>
       <c r="L83" s="3">
         <v>1000</v>
       </c>
       <c r="M83" s="3">
+        <v>1000</v>
+      </c>
+      <c r="N83" s="3">
         <v>900</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>800</v>
-      </c>
-      <c r="O83" s="3">
-        <v>700</v>
       </c>
       <c r="P83" s="3">
         <v>700</v>
       </c>
       <c r="Q83" s="3">
+        <v>700</v>
+      </c>
+      <c r="R83" s="3">
         <v>900</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>1400</v>
-      </c>
-      <c r="S83" s="3">
-        <v>1300</v>
       </c>
       <c r="T83" s="3">
         <v>1300</v>
       </c>
       <c r="U83" s="3">
+        <v>1300</v>
+      </c>
+      <c r="V83" s="3">
         <v>1200</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>4300</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>4400</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>16800</v>
       </c>
-      <c r="Y83" s="3" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="84" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z83" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="84" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5557,8 +5759,11 @@
       <c r="Y84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5628,8 +5833,11 @@
       <c r="Y85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5699,8 +5907,11 @@
       <c r="Y86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5770,8 +5981,11 @@
       <c r="Y87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5841,79 +6055,85 @@
       <c r="Y88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>121100</v>
+      </c>
+      <c r="E89" s="3">
         <v>171400</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>123300</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>186900</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>81300</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>237300</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>143800</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>153800</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>120800</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>111500</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>64800</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>26900</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>225800</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>35300</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>19900</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>49700</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>2800</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-41400</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-74600</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>2200</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-33400</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>94300</v>
       </c>
-      <c r="Y89" s="3" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="90" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z89" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="90" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5939,79 +6159,83 @@
       <c r="W90" s="3"/>
       <c r="X90" s="3"/>
       <c r="Y90" s="3"/>
-    </row>
-    <row r="91" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z90" s="3"/>
+    </row>
+    <row r="91" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-15900</v>
+      </c>
+      <c r="E91" s="3">
         <v>-17800</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-4700</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-15500</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-11300</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-10100</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-8900</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-12000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-2900</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-2300</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-2400</v>
-      </c>
-      <c r="N91" s="3">
-        <v>-700</v>
       </c>
       <c r="O91" s="3">
         <v>-700</v>
       </c>
       <c r="P91" s="3">
+        <v>-700</v>
+      </c>
+      <c r="Q91" s="3">
         <v>-500</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-1300</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-900</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-400</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-800</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-1700</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-2600</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-900</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-2500</v>
       </c>
-      <c r="Y91" s="3" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="92" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z91" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="92" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6081,8 +6305,11 @@
       <c r="Y92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6152,79 +6379,85 @@
       <c r="Y93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-21900</v>
+      </c>
+      <c r="E94" s="3">
         <v>-28600</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-15800</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-44500</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-98100</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-17600</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-8900</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-46500</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-113100</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-2800</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-2400</v>
-      </c>
-      <c r="N94" s="3">
-        <v>-700</v>
       </c>
       <c r="O94" s="3">
         <v>-700</v>
       </c>
       <c r="P94" s="3">
+        <v>-700</v>
+      </c>
+      <c r="Q94" s="3">
         <v>-500</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-1300</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-900</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-400</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-800</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-1700</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-2600</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-700</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-3000</v>
       </c>
-      <c r="Y94" s="3" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="95" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z94" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="95" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6250,8 +6483,9 @@
       <c r="W95" s="3"/>
       <c r="X95" s="3"/>
       <c r="Y95" s="3"/>
-    </row>
-    <row r="96" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z95" s="3"/>
+    </row>
+    <row r="96" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6294,8 +6528,8 @@
       <c r="P96" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="Q96" s="3">
-        <v>0</v>
+      <c r="Q96" s="3" t="s">
+        <v>11</v>
       </c>
       <c r="R96" s="3">
         <v>0</v>
@@ -6321,8 +6555,11 @@
       <c r="Y96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6392,8 +6629,11 @@
       <c r="Y97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6463,8 +6703,11 @@
       <c r="Y98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6534,79 +6777,85 @@
       <c r="Y99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>19800</v>
+      </c>
+      <c r="E100" s="3">
         <v>-500</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-200</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-40500</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-6000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-147200</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-3200</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-17300</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-10000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-2400</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-67500</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-8400</v>
       </c>
-      <c r="O100" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="P100" s="3">
+      <c r="P100" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="Q100" s="3">
         <v>-4800</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-2700</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>4300</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-300</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>6200</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>11600</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-61200</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>34800</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>96300</v>
       </c>
-      <c r="Y100" s="3" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="101" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z100" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="101" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -6649,8 +6898,8 @@
       <c r="P101" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="Q101" s="3">
-        <v>0</v>
+      <c r="Q101" s="3" t="s">
+        <v>11</v>
       </c>
       <c r="R101" s="3">
         <v>0</v>
@@ -6676,75 +6925,81 @@
       <c r="Y101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>118900</v>
+      </c>
+      <c r="E102" s="3">
         <v>142400</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>107300</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>101900</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-22700</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>72600</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>131700</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>90000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-2200</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>106200</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-5100</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>17800</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>225100</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>29900</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>15900</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>53100</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>2100</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-35900</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-64700</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-61500</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>700</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>187600</v>
       </c>
-      <c r="Y102" s="3" t="s">
+      <c r="Z102" s="3" t="s">
         <v>11</v>
       </c>
     </row>
